--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,39 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
   </si>
 </sst>
 </file>
@@ -770,7 +803,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -800,6 +833,98 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920045</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920273</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920286</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920369</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,18 @@
     <t>CHAVEZ</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
@@ -85,6 +97,18 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -95,6 +119,18 @@
   </si>
   <si>
     <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
   </si>
   <si>
     <t>ESDRAS ALAN</t>
@@ -803,7 +839,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -841,10 +877,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -858,22 +894,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920273</v>
+        <v>18330051920022</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -881,22 +917,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920286</v>
+        <v>19330051920067</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -904,24 +940,116 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920369</v>
+        <v>19330051920074</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>18330051920078</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920273</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920286</v>
+      </c>
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920369</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,73 +73,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JOSUE YAMIN</t>
-  </si>
-  <si>
     <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
   </si>
 </sst>
 </file>
@@ -540,19 +480,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>57.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -566,19 +506,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -592,19 +532,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>75.76000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -657,16 +597,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -680,16 +623,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
         <v>28</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>90.31999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -703,16 +649,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>81.81999999999999</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -765,19 +714,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>57.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -791,19 +740,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -817,19 +766,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>75.76000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +788,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -871,186 +820,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920045</v>
+        <v>19330051920273</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>18330051920022</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920067</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920074</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>18330051920078</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920273</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920286</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920369</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
@@ -623,16 +623,16 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>90.31999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="H3">
         <v>7.5</v>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,15 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
   </si>
 </sst>
 </file>
@@ -480,19 +471,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -506,16 +497,16 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H3">
         <v>7.5</v>
@@ -532,10 +523,10 @@
         <v>33</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>3</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -544,7 +535,7 @@
         <v>90.91</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -597,19 +588,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -623,16 +614,16 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>93.55</v>
+        <v>96.77</v>
       </c>
       <c r="H3">
         <v>7.5</v>
@@ -649,19 +640,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>81.81999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -714,19 +705,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>84.20999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -740,10 +731,10 @@
         <v>31</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>30</v>
@@ -766,10 +757,10 @@
         <v>33</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>3</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -778,7 +769,7 @@
         <v>90.91</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -818,29 +809,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920273</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
   </si>
 </sst>
 </file>
@@ -779,7 +788,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -809,6 +818,29 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>18330051920078</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
